--- a/src/Proyectos/P13704-101/Rev_R0/FactorK_48/Espesor_0.075/P13704-101-(14gacr ANSI-61) - K48 - V2-R0.xlsx
+++ b/src/Proyectos/P13704-101/Rev_R0/FactorK_48/Espesor_0.075/P13704-101-(14gacr ANSI-61) - K48 - V2-R0.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\02 - INGENIERIA\BASE DE DATOS PRODUCTOS\ING0006 - P13704-101-(14gacr ANSI-61) - K48 - V2-R0\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\nas.sigrama.com.mx\Maquinados\02 - INGENIERIA\BASE DE DATOS PRODUCTOS\ING0006 - P13704-101-(14gacr ANSI-61) - K48 - V2-R0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:81_{B55DCCD4-D37F-4399-ABEB-0CEB2873D08D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:81_{1C019E4C-9DE9-4B0F-9634-548396F32A3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4785" yWindow="3960" windowWidth="18915" windowHeight="11235" activeTab="1" xr2:uid="{72E190BC-3280-4316-9569-0B2FABF9283B}"/>
+    <workbookView xWindow="7635" yWindow="2670" windowWidth="18915" windowHeight="11235" xr2:uid="{72E190BC-3280-4316-9569-0B2FABF9283B}"/>
   </bookViews>
   <sheets>
     <sheet name="DOBLEZ" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <customWorkbookViews>
-    <customWorkbookView name="Estacion Maquinados - Vista personalizada" guid="{6B774C4D-89BE-4264-AF61-033C95FE9341}" mergeInterval="0" personalView="1" xWindow="319" yWindow="264" windowWidth="1261" windowHeight="749" activeSheetId="1"/>
+    <customWorkbookView name="Estacion Maquinados - Vista personalizada" guid="{6B774C4D-89BE-4264-AF61-033C95FE9341}" mergeInterval="0" personalView="1" xWindow="509" yWindow="178" windowWidth="1261" windowHeight="749" activeSheetId="1"/>
   </customWorkbookViews>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -223,7 +223,7 @@
 </file>
 
 <file path=xl/revisions/revisionHeaders.xml><?xml version="1.0" encoding="utf-8"?>
-<headers xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac" guid="{6D1A242D-D5ED-4223-86DD-2A075525F056}" diskRevisions="1" revisionId="62" version="4">
+<headers xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac" guid="{5BB4029C-8B74-4401-AD12-0247EB70A4DB}" diskRevisions="1" revisionId="62" version="5">
   <header guid="{B07B62A8-5084-4257-895E-0E9D84791666}" dateTime="2026-06-19T16:23:46" maxSheetId="2" userName="Estacion Maquinados" r:id="rId1">
     <sheetIdMap count="1">
       <sheetId val="1"/>
@@ -242,6 +242,12 @@
     </sheetIdMap>
   </header>
   <header guid="{6D1A242D-D5ED-4223-86DD-2A075525F056}" dateTime="2026-06-22T17:55:39" maxSheetId="3" userName="Estacion Maquinados" r:id="rId4" minRId="60" maxRId="62">
+    <sheetIdMap count="2">
+      <sheetId val="1"/>
+      <sheetId val="2"/>
+    </sheetIdMap>
+  </header>
+  <header guid="{5BB4029C-8B74-4401-AD12-0247EB70A4DB}" dateTime="2026-06-25T15:16:12" maxSheetId="3" userName="Estacion Maquinados" r:id="rId5">
     <sheetIdMap count="2">
       <sheetId val="1"/>
       <sheetId val="2"/>
@@ -10019,6 +10025,18 @@
       </border>
     </dxf>
   </rfmt>
+</revisions>
+</file>
+
+<file path=xl/revisions/revisionLog5.xml><?xml version="1.0" encoding="utf-8"?>
+<revisions xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <rfmt sheetId="1" sqref="B2:B33">
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+  </rfmt>
+  <rcv guid="{6B774C4D-89BE-4264-AF61-033C95FE9341}" action="delete"/>
+  <rcv guid="{6B774C4D-89BE-4264-AF61-033C95FE9341}" action="add"/>
 </revisions>
 </file>
 
@@ -10323,7 +10341,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE505A7A-50C9-4874-BF6F-1A89062208EA}">
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.28515625" bestFit="1" customWidth="1"/>
@@ -10335,7 +10353,7 @@
     <col min="8" max="8" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -10349,11 +10367,11 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="1">
         <v>4.2</v>
       </c>
       <c r="C2">
@@ -10363,11 +10381,11 @@
         <v>4.2149999999999999</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="1">
         <v>4.4400000000000004</v>
       </c>
       <c r="C3">
@@ -10377,11 +10395,11 @@
         <v>4.4550000000000001</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="1">
         <v>4.97</v>
       </c>
       <c r="C4">
@@ -10391,11 +10409,11 @@
         <v>4.9850000000000003</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>7</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="1">
         <v>5.78</v>
       </c>
       <c r="C5">
@@ -10405,11 +10423,11 @@
         <v>5.7949999999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>8</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="1">
         <v>6.22</v>
       </c>
       <c r="C6">
@@ -10419,11 +10437,11 @@
         <v>6.2350000000000003</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="1">
         <v>11.29</v>
       </c>
       <c r="C7">
@@ -10433,11 +10451,11 @@
         <v>11.305</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>10</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="1">
         <v>16.22</v>
       </c>
       <c r="C8">
@@ -10447,11 +10465,11 @@
         <v>16.234999999999999</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>11</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="1">
         <v>17.47</v>
       </c>
       <c r="C9">
@@ -10461,11 +10479,11 @@
         <v>17.484999999999999</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>12</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="1">
         <v>18.260000000000002</v>
       </c>
       <c r="C10">
@@ -10475,11 +10493,11 @@
         <v>18.274999999999999</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>13</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="1">
         <v>18.57</v>
       </c>
       <c r="C11">
@@ -10489,11 +10507,11 @@
         <v>18.585000000000001</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>14</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="1">
         <v>21.19</v>
       </c>
       <c r="C12">
@@ -10503,11 +10521,11 @@
         <v>21.204999999999998</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>15</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="1">
         <v>17.47</v>
       </c>
       <c r="C13">
@@ -10517,11 +10535,11 @@
         <v>17.484999999999999</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>16</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="1">
         <v>16.8</v>
       </c>
       <c r="C14">
@@ -10531,11 +10549,11 @@
         <v>16.815000000000001</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>17</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="1">
         <v>4.97</v>
       </c>
       <c r="C15">
@@ -10545,11 +10563,11 @@
         <v>4.9850000000000003</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>18</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="1">
         <v>28.81</v>
       </c>
       <c r="C16">
@@ -10559,11 +10577,11 @@
         <v>28.824999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>19</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="1">
         <v>28.47</v>
       </c>
       <c r="C17">
@@ -10573,11 +10591,11 @@
         <v>28.484999999999999</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>20</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="1">
         <v>20.61</v>
       </c>
       <c r="C18">
@@ -10587,11 +10605,11 @@
         <v>20.625</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>21</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="1">
         <v>20.309999999999999</v>
       </c>
       <c r="C19">
@@ -10601,11 +10619,11 @@
         <v>20.324999999999999</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>22</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="1">
         <v>19.13</v>
       </c>
       <c r="C20">
@@ -10615,11 +10633,11 @@
         <v>19.145</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>23</v>
       </c>
-      <c r="B21">
+      <c r="B21" s="1">
         <v>15.99</v>
       </c>
       <c r="C21">
@@ -10629,11 +10647,11 @@
         <v>16.004999999999999</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>24</v>
       </c>
-      <c r="B22">
+      <c r="B22" s="1">
         <v>12.83</v>
       </c>
       <c r="C22">
@@ -10643,11 +10661,11 @@
         <v>12.845000000000001</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>25</v>
       </c>
-      <c r="B23">
+      <c r="B23" s="1">
         <v>9.69</v>
       </c>
       <c r="C23">
@@ -10657,11 +10675,11 @@
         <v>9.7050000000000001</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>26</v>
       </c>
-      <c r="B24">
+      <c r="B24" s="1">
         <v>8.5</v>
       </c>
       <c r="C24">
@@ -10671,11 +10689,11 @@
         <v>8.5150000000000006</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>27</v>
       </c>
-      <c r="B25">
+      <c r="B25" s="1">
         <v>1.23</v>
       </c>
       <c r="C25">
@@ -10685,11 +10703,11 @@
         <v>1.2450000000000001</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>28</v>
       </c>
-      <c r="B26">
+      <c r="B26" s="1">
         <v>0.5</v>
       </c>
       <c r="C26">
@@ -10699,11 +10717,11 @@
         <v>0.51500000000000001</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>29</v>
       </c>
-      <c r="B27">
+      <c r="B27" s="1">
         <v>0.25</v>
       </c>
       <c r="C27">
@@ -10713,11 +10731,11 @@
         <v>0.26500000000000001</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>30</v>
       </c>
-      <c r="B28">
+      <c r="B28" s="1">
         <v>0.75</v>
       </c>
       <c r="C28">
@@ -10727,11 +10745,11 @@
         <v>0.76500000000000001</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>31</v>
       </c>
-      <c r="B29">
+      <c r="B29" s="1">
         <v>2.8</v>
       </c>
       <c r="C29">
@@ -10741,11 +10759,11 @@
         <v>2.8149999999999999</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>32</v>
       </c>
-      <c r="B30">
+      <c r="B30" s="1">
         <v>14.17</v>
       </c>
       <c r="C30">
@@ -10755,11 +10773,11 @@
         <v>14.185</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>33</v>
       </c>
-      <c r="B31">
+      <c r="B31" s="1">
         <v>2.95</v>
       </c>
       <c r="C31">
@@ -10769,11 +10787,11 @@
         <v>2.9649999999999999</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>34</v>
       </c>
-      <c r="B32">
+      <c r="B32" s="1">
         <v>0.25</v>
       </c>
       <c r="C32">
@@ -10783,11 +10801,11 @@
         <v>0.26500000000000001</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>35</v>
       </c>
-      <c r="B33">
+      <c r="B33" s="1">
         <v>8.2100000000000009</v>
       </c>
       <c r="C33">
@@ -10797,24 +10815,25 @@
         <v>8.2249999999999996</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25"/>
   </sheetData>
   <customSheetViews>
     <customSheetView guid="{6B774C4D-89BE-4264-AF61-033C95FE9341}">
-      <selection activeCell="K9" sqref="K9"/>
+      <selection activeCell="F13" sqref="F13"/>
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+      <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
     </customSheetView>
   </customSheetViews>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD517692-E68F-458A-8D3B-FD080AF57816}">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>36</v>
       </c>
@@ -10831,7 +10850,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -10848,7 +10867,7 @@
         <v>29.866</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -10865,7 +10884,7 @@
         <v>22.492999999999999</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -10882,7 +10901,7 @@
         <v>0.32500000000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -10899,7 +10918,7 @@
         <v>20.704999999999998</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -10916,7 +10935,7 @@
         <v>11.824999999999999</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -10933,7 +10952,7 @@
         <v>13.835000000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -10950,7 +10969,7 @@
         <v>0.20499999999999999</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -10967,7 +10986,6 @@
         <v>0.23300000000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25"/>
   </sheetData>
   <customSheetViews>
     <customSheetView guid="{6B774C4D-89BE-4264-AF61-033C95FE9341}">
